--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="85">
   <si>
     <t>Mat</t>
   </si>
@@ -67,87 +67,99 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>PERALTA</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>ALJAVID</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>PAYAN</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>ALJAVID</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>RASCON</t>
+  </si>
+  <si>
+    <t>ISLAS</t>
+  </si>
+  <si>
     <t>TRONCO</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
     <t>VALENTE</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>RASCON</t>
-  </si>
-  <si>
     <t>MERINO</t>
   </si>
   <si>
@@ -160,100 +172,103 @@
     <t>CHIPAHUA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>GAYTAN</t>
   </si>
   <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
     <t>LLAVE</t>
   </si>
   <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>VICTOR ALEXIS</t>
+  </si>
+  <si>
+    <t>VICTOR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JONATHAN ISRAEL</t>
+  </si>
+  <si>
     <t>SANTIAGO ZURIEL</t>
   </si>
   <si>
+    <t>ANGEL BRYAN</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>CRISTIAN YAIR</t>
+    <t>IVANNA GUADALUPE</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>HELI SAMUEL</t>
+  </si>
+  <si>
+    <t>JOSMAR RENE</t>
+  </si>
+  <si>
+    <t>JAZMIN ISABEL</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>CHRISTIAN</t>
+  </si>
+  <si>
+    <t>CARLOS JARE</t>
+  </si>
+  <si>
+    <t>DIEGO GIOVANI</t>
+  </si>
+  <si>
+    <t>MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FERNANDO</t>
+  </si>
+  <si>
+    <t>CESAR GUADALUPE</t>
+  </si>
+  <si>
+    <t>KEVIN URIEL</t>
+  </si>
+  <si>
+    <t>ALESSANDRO CALEB</t>
+  </si>
+  <si>
+    <t>CARLOS ALEXANDER</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>ADBIEL</t>
   </si>
   <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>VICTOR ALEXIS</t>
-  </si>
-  <si>
-    <t>HELI SAMUEL</t>
-  </si>
-  <si>
-    <t>JOSMAR RENE</t>
-  </si>
-  <si>
-    <t>JAZMIN ISABEL</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>CHRISTIAN</t>
-  </si>
-  <si>
-    <t>CARLOS JARE</t>
-  </si>
-  <si>
-    <t>DIEGO GIOVANI</t>
-  </si>
-  <si>
-    <t>MONTSERRAT</t>
-  </si>
-  <si>
-    <t>CESAR GUADALUPE</t>
-  </si>
-  <si>
-    <t>JONATHAN ISRAEL</t>
-  </si>
-  <si>
-    <t>KEVIN URIEL</t>
-  </si>
-  <si>
-    <t>ANGEL BRYAN</t>
-  </si>
-  <si>
-    <t>ALESSANDRO CALEB</t>
-  </si>
-  <si>
-    <t>CARLOS ALEXANDER</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>IVANNA GUADALUPE</t>
-  </si>
-  <si>
     <t>ISA ANGELICA</t>
   </si>
   <si>
     <t>JORGE LUIS</t>
+  </si>
+  <si>
+    <t>YAEL</t>
   </si>
   <si>
     <t>JUAN ALEXIS</t>
@@ -800,7 +815,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -832,16 +847,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920111</v>
+        <v>24330051920063</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -855,7 +870,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920314</v>
+        <v>24330051920337</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -864,7 +879,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -878,16 +893,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920071</v>
+        <v>24330051920334</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -901,16 +916,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920084</v>
+        <v>24330051920109</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -924,16 +939,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920070</v>
+        <v>24330051920111</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -942,21 +957,21 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920063</v>
+        <v>24330051920062</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -965,21 +980,21 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920337</v>
+        <v>24330051920314</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -988,21 +1003,21 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920074</v>
+        <v>24330051920068</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1011,21 +1026,21 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920077</v>
+        <v>24330051920070</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1039,16 +1054,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920067</v>
+        <v>24330051920074</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1062,16 +1077,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920082</v>
+        <v>24330051920077</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1085,16 +1100,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920268</v>
+        <v>24330051920067</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1108,16 +1123,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920080</v>
+        <v>24330051920082</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1131,16 +1146,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920339</v>
+        <v>24330051920268</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1154,16 +1169,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920064</v>
+        <v>24330051920080</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1177,16 +1192,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920069</v>
+        <v>24330051920339</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1200,16 +1215,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920066</v>
+        <v>24330051920064</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1223,16 +1238,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920109</v>
+        <v>24330051920069</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1246,16 +1261,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920076</v>
+        <v>24330051920036</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1269,16 +1284,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920062</v>
+        <v>24330051920066</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1292,16 +1307,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920034</v>
+        <v>24330051920076</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1315,16 +1330,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920079</v>
+        <v>24330051920034</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1338,16 +1353,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920083</v>
+        <v>24330051920079</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1361,16 +1376,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920068</v>
+        <v>24330051920083</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1384,16 +1399,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920081</v>
+        <v>24330051920084</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1407,16 +1422,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920075</v>
+        <v>24330051920081</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1430,24 +1445,70 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
+        <v>24330051920075</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>24330051920072</v>
+      </c>
+      <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
         <v>24330051920078</v>
       </c>
-      <c r="B28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
         <v>27</v>
       </c>
-      <c r="D28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28">
+      <c r="D30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="88">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>TZITZIHUA</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>ALJAVID</t>
   </si>
   <si>
@@ -157,6 +160,9 @@
     <t>OSORIO</t>
   </si>
   <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -209,6 +215,9 @@
   </si>
   <si>
     <t>IVANNA GUADALUPE</t>
+  </si>
+  <si>
+    <t>DAVID</t>
   </si>
   <si>
     <t>GABRIELA</t>
@@ -815,7 +824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -853,10 +862,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -876,10 +885,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -899,10 +908,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -922,10 +931,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -945,10 +954,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -968,10 +977,10 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -991,10 +1000,10 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1014,10 +1023,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1031,16 +1040,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920070</v>
+        <v>24330051920299</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1049,21 +1058,21 @@
         <v>9</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920074</v>
+        <v>24330051920070</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1077,16 +1086,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920077</v>
+        <v>24330051920074</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1100,16 +1109,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920067</v>
+        <v>24330051920077</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1123,16 +1132,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920082</v>
+        <v>24330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1146,16 +1155,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920268</v>
+        <v>24330051920082</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1169,16 +1178,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920080</v>
+        <v>24330051920268</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1192,16 +1201,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920339</v>
+        <v>24330051920080</v>
       </c>
       <c r="B17" t="s">
         <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1215,16 +1224,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920064</v>
+        <v>24330051920339</v>
       </c>
       <c r="B18" t="s">
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1238,16 +1247,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920069</v>
+        <v>24330051920064</v>
       </c>
       <c r="B19" t="s">
         <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1261,16 +1270,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920036</v>
+        <v>24330051920069</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1284,16 +1293,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920066</v>
+        <v>24330051920036</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1307,16 +1316,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920076</v>
+        <v>24330051920066</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1330,16 +1339,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920034</v>
+        <v>24330051920076</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1353,16 +1362,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920079</v>
+        <v>24330051920034</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1376,16 +1385,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920083</v>
+        <v>24330051920079</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1399,16 +1408,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920084</v>
+        <v>24330051920083</v>
       </c>
       <c r="B26" t="s">
         <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1422,16 +1431,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920081</v>
+        <v>24330051920084</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1445,16 +1454,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920075</v>
+        <v>24330051920081</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1468,16 +1477,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920072</v>
+        <v>24330051920075</v>
       </c>
       <c r="B29" t="s">
         <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1491,16 +1500,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920078</v>
+        <v>24330051920072</v>
       </c>
       <c r="B30" t="s">
         <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1509,6 +1518,29 @@
         <v>9</v>
       </c>
       <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>24330051920078</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>PARADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>MARCO DIDIEL</t>
   </si>
 </sst>
 </file>
@@ -477,7 +486,7 @@
         <v>87.8</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -542,7 +551,7 @@
         <v>90.23999999999999</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -607,7 +616,7 @@
         <v>90.23999999999999</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -647,6 +656,29 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>24330051920404</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
@@ -676,7 +676,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
+++ b/docentes/Loyo Sanchez Raul Manuel - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,15 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>PARADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>MARCO DIDIEL</t>
   </si>
 </sst>
 </file>
@@ -607,16 +598,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>90.23999999999999</v>
+        <v>97.56</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -626,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -656,29 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>24330051920404</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
